--- a/client_data/client_001/leads.xlsx
+++ b/client_data/client_001/leads.xlsx
@@ -531,29 +531,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>salons in Jodhpur</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fitness Pulse Gym</t>
+          <t>Expose Salon</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Kalwar Rd, Suraj Nagar, Jhotwara, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302012, India</t>
+          <t>9th A Road Near Kothi Heritage Near Gypsy Family Dhaba, near HDFC bank, Sardarpura, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342001, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>098870 00058</t>
+          <t>089490 68844</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1915</v>
+        <v>3736</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -572,29 +572,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>salons in Jaipur</t>
+          <t>clinics in Udaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Unisex Salon By Nidhi</t>
+          <t>Redefine Aesthetics Clinic Udaipur</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>34-A,Raghu Vihar Vistar,Near VT Road, Chauraha, Patrkar Road, Mansarovar, Jaipur, Rajasthan 302020, India</t>
+          <t>First Floor, Vinayak Complex-B, 19, Durga Nursery Rd, Shiv Park Colony, Compex, Shakti Nagar, Udaipur, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>098871 81819</t>
+          <t>078788 50277</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1405</v>
+        <v>2736</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -613,29 +613,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Shree Natwar Hair &amp; skin care Family salon</t>
+          <t>Fitness Pro Elite Mansarovar</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Shop 4, 5, New Navratan Rd, near Eden Court, Bedla, Udaipur, Bhuwana, Rajasthan 313001, India</t>
+          <t>near IPS School, Shanthi Nagar B, Shanthi Nagar, Mansarovar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>098280 82922</t>
+          <t>093144 55664</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1230</v>
+        <v>1515</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -654,29 +654,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Champion Hair Salon</t>
+          <t>KLEAN FIT Iconic C-SCHEME</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>shrinath colony, Under Hotel Riviera, near pulla pullia, New Flora Complex Colony, Pulla Bhuwana, road, Udaipur, Udaipur (M Corp.) (Part), Rajasthan 313001, India</t>
+          <t>3rd Floor, Crystal Palm Mall, 22 Godown Circle, Sardar Patel Marg, near Nehru Sahkar Bhavan, Shivaji Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>096490 88841</t>
+          <t>090246 62515</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1067</v>
+        <v>885</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -695,29 +695,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Champion Gal's Spa &amp; Man's salon</t>
+          <t>Strength Nation Fitness Club Gym</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>M.G. Colllege Road, Near hanuman Temple, Sardarpura, Bhopalpura, Udaipur, Rajasthan 313001, India</t>
+          <t>297, Block-B, extension scheme, opposite to women Police Station, near Chitrakoot Nagar, Shyam Nagar, Bhuwana, Raghunathpura, Roopnagar, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>097990 88841</t>
+          <t>073401 81213</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>824</v>
+        <v>696</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -736,29 +736,29 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>salons in Jodhpur</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Lifetime Fitness Club</t>
+          <t>MUKTA SALON - Hair, Nails, Beauty and Makeup Salon in jodhpur</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3rd Floor, at V Cube, Plot no. 1-6, opp. Gaurav Tower Marg, Kalyan Colony, D-Block, Malviya Nagar, Jaipur, Rajasthan 302017, India</t>
+          <t>Showroom number 3, 1st C Rd, opposite to Arrora chaat, Sardarpura, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>099505 50885</t>
+          <t>095113 30208</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>754</v>
+        <v>523</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -777,29 +777,29 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>salons in Jodhpur</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Vaidavya Hair Salon</t>
+          <t>Styling Station Salon &amp; Academy</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>196, Garh Magri, Pulla Bhuwana, Shobhagpura, Udaipur, Sobhagpura, Rajasthan 313001, India</t>
+          <t>9th D Rd, near Hdfc bank, near Zudio, Sardarpura, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>098879 96116</t>
+          <t>079766 70796</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>542</v>
+        <v>499</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -818,29 +818,29 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>clinics in Udaipur</t>
+          <t>salons in Jodhpur</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Dr Nilesh Patira jain physician✅ BEST PHYSICIAN IN TOWN</t>
+          <t>Big Boss Unisex Salon</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>TRIVANTA hospital Near hotel Howard Johnson Meera nagar, C Block, Pahada, Udaipur, Bhuwana, Rajasthan 313001, India</t>
+          <t>Jalori Gate Circle, near bhati softy n softy, Jalori Bari, Bhistiyon Ka Bas, Jodhpur, Rajasthan 342001, India</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>088241 82649</t>
+          <t>075681 64935</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>414</v>
+        <v>452</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -859,29 +859,29 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Bounce Salon &amp; Makeover Studio</t>
+          <t>The Workout Wala</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>First floor,Centrum, HMXR+QH6, Sukhadia Cir, above Shivam optical, New Fatehpura, Panchwati, Udaipur, Rajasthan 313004, India</t>
+          <t>Woodland Square, Amal Ka Kanta Rd, near Police Thana, Kanji Ka Hata, Surajpole, Brahmpuri, Udaipur, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>073578 33111</t>
+          <t>099504 71921</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -900,29 +900,29 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sparsh View Salon &amp; Academy</t>
+          <t>Delta Fitness</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>F1, FIRST FLOOR, SHOBHAGPURA CIRCLE, GIRWA, 100 Feet Rd, Pulla Bhuwana, Shobhagpura, Udaipur, Sobhagpura, Rajasthan 313001, India</t>
+          <t>30/31, Gokul Village Rd, Rk puram, Sector 9, Udaipur, Gordhan Vilas Rural, Rajasthan 313002, India</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>073001 11484</t>
+          <t>077428 09982</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>399</v>
+        <v>331</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -946,24 +946,24 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Looks Salon - Urban Square Mall Udaipur</t>
+          <t>Ftv London salon academy Udaipur</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Mini Anchor-2, First Floor, Urban Square Mall, Udyog Vihar, Plot No. F - 210 to 223, Gaurav Path, RICO industrial area, Suker, Udaipur, Rajasthan 313001, India</t>
+          <t>2nd floor, of Royal Enfield showroom, 100 Feet Rd, Pulla Bhuwana, Shobhagpura, Udaipur, Sobhagpura, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>096496 45133</t>
+          <t>073000 02997</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>322</v>
+        <v>288</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -982,29 +982,29 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>salons in Jaipur</t>
+          <t>salons in Jodhpur</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>The tony's hair &amp;beauty unisex salon</t>
+          <t>The style room Unisex salon</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Shop no 56, gate no. 2, Sardar Patel Marg, opposite BSNL office, Patel Colony, Hathroi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>kalpatru shopping center, in front of sandeep tiles, Sindhi Colony, Sector-E, Shastri Nagar, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342001, India</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>087428 79416</t>
+          <t>073000 09290</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -1023,29 +1023,29 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Burnfit gym | Best Gym In Jaipur</t>
+          <t>Gym World</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Plot no. A-7, behind Mehta book depo, Telephone Colony, Bank Colony, Gopal Pura Mode, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302015, India</t>
+          <t>301, Creative Plaza, University Rd, North Ayad, Ayad, Pahada, Udaipur, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>082906 01516</t>
+          <t>098281 12123</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>248</v>
+        <v>198</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -1064,29 +1064,29 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Let's Burn Gym</t>
+          <t>Reshape Fitness gym</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>B, arghan, first floor, TOWER-1, plot no R6, Sector 2, Sector-1, Vidyadhar Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302029, India</t>
+          <t>Rehsape fitness gym, City Shine Complex, 4 gokul pura, University Rd, above Biryani by kilo, Pahada, Udaipur, Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>099283 44474</t>
+          <t>091666 41343</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>244</v>
+        <v>173</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -1105,29 +1105,29 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>clinics in Jaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Aura Skin &amp; Health Clinic</t>
+          <t>Strong Fit Gym</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>J-108, Ashok Chowk, Adarsh Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302004, India</t>
+          <t>Rishi Nagar, 100 Feet Road, Sector No. 3, near Makkhan Kitchens, Shanti Nagar, Sector 3, Hiran Magri, Udaipur, Rajasthan 313002, India</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>084400 66723</t>
+          <t>082092 80252</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>219</v>
+        <v>99</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -1146,70 +1146,74 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>salons in Jodhpur</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>The Shyam Salon and Academy</t>
+          <t>Yantra Salon - A Family Salon | Hair | Makeup | Skin | Nails</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>opposite coffee culture cafe, Ratneshwar Colony, Pulla Bhuwana, Shobhagpura, Udaipur, Sobhagpura, Rajasthan 313001, India</t>
+          <t>Akhaliya Circle, near ICICI Bank, 1st Pulia, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>082090 76837</t>
+          <t>0291 276 0050</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>1942</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yantrasalonjodhpur</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Monsoon Salon</t>
+          <t>JK THE MEDICAL GYM</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>56, First Floor, Amrit Shree, Ashok Nagar Main Rd, Digamber Jain Mandir, Shakti Nagar, Udaipur, Rajasthan 313002, India</t>
+          <t>Krishna Vatika, Near, RK Circle, Pulan, Pulla Bhuwana, Rupsagar, Udaipur, Udaipur (M Corp.) (Part), Rajasthan 313001, India</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>080060 60606</t>
+          <t>099289 81863</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>669</v>
+        <v>525</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
@@ -1223,7 +1227,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/monsoonsalon.udaipur?igsh=aTVkZTZ6N3pkMnd3</t>
+          <t>https://www.instagram.com/jkmedicalgym?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1232,29 +1236,29 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>salons in Jodhpur</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FitLife Gym Vaishali Nagar</t>
+          <t>Posshe Salons</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4th Floor, Oppo- Khandelwal Dhabawalas, South, Gandhi Path Rd, Girnar Colony, Girnar Colony South, Chitrakoot, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302021, India</t>
+          <t>Near Goru Sweet Home Street, B Rd, Sardarpura, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>076888 91224</t>
+          <t>078779 81454</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>316</v>
+        <v>404</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
@@ -1268,7 +1272,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitlifegym_vaishalinagar?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
+          <t>https://www.instagram.com/posshesalonsjodhpur/</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -1277,29 +1281,29 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>gyms in Udaipur</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Sweatup - The Luxury Gym</t>
+          <t>Pro Fitness Studio</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>E-10, Gautam Marg, Amrapali Circle, Vaishali Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302021, India</t>
+          <t>338, Madri industry road, U.L.T.Colony, Udaipur, Rajasthan 313003, India</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>070822 40402</t>
+          <t>096022 33710</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>315</v>
+        <v>160</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
@@ -1313,7 +1317,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sweatup__theluxurygym/</t>
+          <t>https://www.instagram.com/pro_fitness_studio_1.0?igsh=eDAzY2YwemFlN3Jj</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1327,24 +1331,24 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Sky Fitness - Best Gym in Mangyawas, Mansarovar, Jaipur</t>
+          <t>Sky Fitness - Best Gym In Ajmer Road, Jaipur</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Maharani Garden Road, Mansarover, Rajat Path, Jaipur, Rajasthan 302020, India</t>
+          <t>1st Floor, ML Tower, Metro Piller No-01, Teja Circle, Gopalpura Bypass Rd, near Drom Marbel, Mohan Nagar, Mohru Nagar, Mansarovar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302020, India</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>095880 37686</t>
+          <t>075687 98310</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>187</v>
+        <v>118</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -1358,7 +1362,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/skyfitnessjaipur</t>
+          <t>https://www.instagram.com/skyfitnessjaipur1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>

--- a/client_data/client_001/leads.xlsx
+++ b/client_data/client_001/leads.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$L$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -469,6 +469,7 @@
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -519,10 +520,15 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>E-commerce Platform</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Weak Points</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PageSpeed Score (mobile)</t>
         </is>
@@ -536,24 +542,24 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Expose Salon</t>
+          <t>Super Star unisex Salon</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>9th A Road Near Kothi Heritage Near Gypsy Family Dhaba, near HDFC bank, Sardarpura, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342001, India</t>
+          <t>E-23, Near Mayur Plastics, Shopping Center Rd, behind Petrol Pump, opp. Manidhari Hospital, Sindhi Colony, Sector-E, Shastri Nagar, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>089490 68844</t>
+          <t>094137 82803</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3736</v>
+        <v>1604</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -568,33 +574,34 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>clinics in Udaipur</t>
+          <t>gyms in Jaipur</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Redefine Aesthetics Clinic Udaipur</t>
+          <t>Ram's Fitness Club IMPACT</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>First Floor, Vinayak Complex-B, 19, Durga Nursery Rd, Shiv Park Colony, Compex, Shakti Nagar, Udaipur, Rajasthan 313001, India</t>
+          <t>111/14, Mangalam, Sector 11 Rd, Kumbha Marg, Sanganer, Sector 11, Pratap Nagar, Jaipur, Rajasthan 302033, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>078788 50277</t>
+          <t>097722 78888</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2736</v>
+        <v>1281</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -609,33 +616,34 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>salons in Jaipur</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Fitness Pro Elite Mansarovar</t>
+          <t>K Factor Salon</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>near IPS School, Shanthi Nagar B, Shanthi Nagar, Mansarovar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
+          <t>157, Ayodhya Path, Saket Nagar, Shyam Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302019, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>093144 55664</t>
+          <t>096806 56581</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1515</v>
+        <v>713</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -650,33 +658,34 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>gyms in Jodhpur</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KLEAN FIT Iconic C-SCHEME</t>
+          <t>Pulse Fitness Jodhpur</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3rd Floor, Crystal Palm Mall, 22 Godown Circle, Sardar Patel Marg, near Nehru Sahkar Bhavan, Shivaji Nagar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302001, India</t>
+          <t>117/4 yes bank basement bhairav circle, Ratanada, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>090246 62515</t>
+          <t>097821 26677</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>885</v>
+        <v>611</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -691,33 +700,34 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>gyms in Udaipur</t>
+          <t>gyms in Jodhpur</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Strength Nation Fitness Club Gym</t>
+          <t>ATHLETIC GYM AND FITNESS CENTER</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>297, Block-B, extension scheme, opposite to women Police Station, near Chitrakoot Nagar, Shyam Nagar, Bhuwana, Raghunathpura, Roopnagar, Rajasthan 313001, India</t>
+          <t>33 MEERA NAGAR, CIRCLE, near SR SCHOOL, Jhalamand, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342005, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>073401 81213</t>
+          <t>096021 00698</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>696</v>
+        <v>389</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -732,33 +742,34 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>salons in Jodhpur</t>
+          <t>gyms in Jodhpur</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>MUKTA SALON - Hair, Nails, Beauty and Makeup Salon in jodhpur</t>
+          <t>BOSSFIT NEW LEVEL OF FITNESS</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Showroom number 3, 1st C Rd, opposite to Arrora chaat, Sardarpura, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
+          <t>80 Feet Road, opp. PF Office 87, Shankar Nagar, Katariya Choukha, Bhadu Market, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342008, India</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>095113 30208</t>
+          <t>095497 86143</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>523</v>
+        <v>380</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -773,33 +784,34 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>salons in Jodhpur</t>
+          <t>gyms in Jodhpur</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Styling Station Salon &amp; Academy</t>
+          <t>EQUINIX FITNESS JODHPUR</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9th D Rd, near Hdfc bank, near Zudio, Sardarpura, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
+          <t>30, New Power House Rd, near SIS, Sector-H, security, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342001, India</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>079766 70796</t>
+          <t>098285 06359</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>499</v>
+        <v>352</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -814,33 +826,34 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>salons in Jodhpur</t>
+          <t>salons in Jaipur</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Big Boss Unisex Salon</t>
+          <t>Style &amp; Beauty World</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Jalori Gate Circle, near bhati softy n softy, Jalori Bari, Bhistiyon Ka Bas, Jodhpur, Rajasthan 342001, India</t>
+          <t>station road, Flyover, near Jtm Mall, Income Tax Colony, Model Town, Jagatpura, Jaipur, Rajasthan 302017, India</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>075681 64935</t>
+          <t>088900 90042</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>452</v>
+        <v>304</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -855,33 +868,34 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>gyms in Udaipur</t>
+          <t>gyms in Jodhpur</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>The Workout Wala</t>
+          <t>Sky Fit Gym Sardarpura</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Woodland Square, Amal Ka Kanta Rd, near Police Thana, Kanji Ka Hata, Surajpole, Brahmpuri, Udaipur, Rajasthan 313001, India</t>
+          <t>3rd A Rd, Sardarpura, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342001, India</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>099504 71921</t>
+          <t>081122 11437</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>413</v>
+        <v>230</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -896,33 +910,34 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>gyms in Udaipur</t>
+          <t>gyms in Jodhpur</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Delta Fitness</t>
+          <t>POWER CLUB</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30/31, Gokul Village Rd, Rk puram, Sector 9, Udaipur, Gordhan Vilas Rural, Rajasthan 313002, India</t>
+          <t>Plot no 929, 9th E Rd, Sardarpura, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342001, India</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>077428 09982</t>
+          <t>094143 01716</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>331</v>
+        <v>116</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -937,33 +952,34 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>salons in Udaipur</t>
+          <t>gyms in Jodhpur</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Ftv London salon academy Udaipur</t>
+          <t>HR Health Club</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2nd floor, of Royal Enfield showroom, 100 Feet Rd, Pulla Bhuwana, Shobhagpura, Udaipur, Sobhagpura, Rajasthan 313001, India</t>
+          <t>5th B Rd, near Plant Story Restaurant, Agarwal Ki Bagechi, Sardarpura, Jodhpur, Rajasthan 342001, India</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>073000 02997</t>
+          <t>084400 70555</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -978,33 +994,34 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>salons in Jodhpur</t>
+          <t>gyms in Jodhpur</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>The style room Unisex salon</t>
+          <t>Maxfit Premium</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>kalpatru shopping center, in front of sandeep tiles, Sindhi Colony, Sector-E, Shastri Nagar, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342001, India</t>
+          <t>Plot no 7, Pal Rd, near chungi chauki, Bhadu Market, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>073000 09290</t>
+          <t>089520 80780</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -1019,33 +1036,34 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>gyms in Udaipur</t>
+          <t>clinics in Jodhpur</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Gym World</t>
+          <t>DR ALOK GUPTA CLINIC</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>301, Creative Plaza, University Rd, North Ayad, Ayad, Pahada, Udaipur, Rajasthan 313001, India</t>
+          <t>16-E-4, 5th Puliya Rd, opposite Jeevan Jyoti Hospital, Chopasni Housing Board, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>098281 12123</t>
+          <t>094602 14664</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -1060,33 +1078,34 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>gyms in Udaipur</t>
+          <t>clinics in Jodhpur</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Reshape Fitness gym</t>
+          <t>VRINDA FACE AND SUPERSPECIALITY DENTAL IMPLANT CENTER | BEST DENTAL HOSPITAL IN JODHPUR | SMILE DESIGN HOSPITAL</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Rehsape fitness gym, City Shine Complex, 4 gokul pura, University Rd, above Biryani by kilo, Pahada, Udaipur, Rajasthan 313001, India</t>
+          <t>9-A, Main Pal Road, Opp. Hanwant School, Dalle Khan Chakki Circle, Baldev Nagar, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342001, India</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>091666 41343</t>
+          <t>096362 96636</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>173</v>
+        <v>64</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -1101,47 +1120,53 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>gyms in Udaipur</t>
+          <t>salons in Jaipur</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Strong Fit Gym</t>
+          <t>Saundarya beauty salon</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Rishi Nagar, 100 Feet Road, Sector No. 3, near Makkhan Kitchens, Shanti Nagar, Sector 3, Hiran Magri, Udaipur, Rajasthan 313002, India</t>
+          <t>6-A, Behind Maharwal Optical, Behind Vidhan Sabha Lal Kothi, Janpath Road, Friends Colony, Satya Vihar, Friends Colony, Krishna Nagar II, Lalkothi, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302015, India</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>082092 80252</t>
+          <t>098290 23927</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>1241</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/saundaryabeautysalon?igsh=dzJ4ZnZxd25zNjdt</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1151,24 +1176,24 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Yantra Salon - A Family Salon | Hair | Makeup | Skin | Nails</t>
+          <t>Afeem Spa &amp; Salon</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Akhaliya Circle, near ICICI Bank, 1st Pulia, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
+          <t>Opp Passport Office, Main, Pal Rd, near N S Garden, Jodhpur, 342003, Pal Rd, Narpat Nagar, Ashok Nagar, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342008, India</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0291 276 0050</t>
+          <t>070146 32226</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1942</v>
+        <v>715</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
@@ -1182,38 +1207,39 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yantrasalonjodhpur</t>
+          <t>https://www.instagram.com/afeemspaandsalon/</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>gyms in Udaipur</t>
+          <t>gyms in Jodhpur</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>JK THE MEDICAL GYM</t>
+          <t>NRM FITNESS</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Krishna Vatika, Near, RK Circle, Pulan, Pulla Bhuwana, Rupsagar, Udaipur, Udaipur (M Corp.) (Part), Rajasthan 313001, India</t>
+          <t>7X2H+3CQ, Keshavnagar, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342008, India</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>099289 81863</t>
+          <t>098283 50520</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
@@ -1227,38 +1253,39 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jkmedicalgym?utm_source=ig_web_button_share_sheet&amp;igsh=ZDNlZDc0MzIxNw==</t>
+          <t>https://instagram.com/thenrmgym?igshid=MmVlMjlkMTBhMg==</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>salons in Jodhpur</t>
+          <t>clinics in Udaipur</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Posshe Salons</t>
+          <t>Aura Skin and Hair Clinic</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Near Goru Sweet Home Street, B Rd, Sardarpura, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
+          <t>221, Hanuman Mandir Vali Gali, Sardarpura, Udaipur, Rajasthan 313004, India</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>078779 81454</t>
+          <t>097855 00336</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>404</v>
+        <v>511</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
@@ -1272,38 +1299,39 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/posshesalonsjodhpur/</t>
+          <t>http://www.facebook.com/auraskinandhairclinic/</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>gyms in Udaipur</t>
+          <t>gyms in Jodhpur</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Pro Fitness Studio</t>
+          <t>Gym NAKA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>338, Madri industry road, U.L.T.Colony, Udaipur, Rajasthan 313003, India</t>
+          <t>2, 3, Electronic Complex, EC-1, near Steel Bhawan, opp. Fresh &amp; Green, Sector G, Shastri Nagar, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342003, India</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>096022 33710</t>
+          <t>089551 21272</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>160</v>
+        <v>485</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
@@ -1317,38 +1345,39 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pro_fitness_studio_1.0?igsh=eDAzY2YwemFlN3Jj</t>
+          <t>https://www.facebook.com/gymnaka/</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>gyms in Jaipur</t>
+          <t>gyms in Jodhpur</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Sky Fitness - Best Gym In Ajmer Road, Jaipur</t>
+          <t>Pro Fitness Health Club - Best Gym in Sardarpura | Best Fitness Centre in Sardarpura</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1st Floor, ML Tower, Metro Piller No-01, Teja Circle, Gopalpura Bypass Rd, near Drom Marbel, Mohan Nagar, Mohru Nagar, Mansarovar, Jaipur, Jaipur Nagar Nigam Area, Rajasthan 302020, India</t>
+          <t>2nd Floor, Moti Mahal Tower, 10th B Rd, Near Children Park, Sardarpura, Jodhpur, Jodhpur-South (M Corp.), Rajasthan 342001, India</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>075687 98310</t>
+          <t>077340 08474</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -1362,14 +1391,15 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/skyfitnessjaipur1</t>
+          <t>https://www.instagram.com/profitnessjodhpur/</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K21"/>
+  <autoFilter ref="A1:L21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>